--- a/secure_report/reports/テスト項目書_20260630.xlsx
+++ b/secure_report/reports/テスト項目書_20260630.xlsx
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3714,6 +3714,177 @@
         </is>
       </c>
       <c r="L45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>XSS-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XSS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>受講者サイト</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ヘッダー・サイドバー（ログイン後全ページ）cp-content テンプレート</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>#B（cp-content）</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>① DBで受講者の氏名フィールドに `&lt;script&gt;alert('XSS-17')&lt;/script&gt;` を書き込む ▸ ② そのアカウントでログインし、受講者サイトのヘッダー・サイドバーが表示されるページを開く ▸ ③ ヘッダーの氏名欄でJavaScriptアラートが発生しないことを確認する ▸ ④ HTMLソースで `htmlspecialchars()` によりエスケープされていることを確認する</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>`テスト&lt;script&gt;alert('XSS-17')&lt;/script&gt;` ※ DB user.name フィールドに設定</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>アラートが発生しない。ヘッダー・サイドバーの氏名が `&amp;lt;script&amp;gt;` にエスケープされて表示される</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>cp-content 補足資料対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>XSS-18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>XSS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>受講者サイト</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ニュース一覧 `/archives/category/news/`（cp-content: category.php）</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>#C（cp-content）</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>① CMS または DB で WordPress 投稿のタイトルフィールドに `&lt;img src=x onerror=alert('XSS-18')&gt;` を書き込む ▸ ② 受講者サイトのニュース一覧 `/archives/category/news/` にアクセスする ▸ ③ ニュースタイトル表示欄でJavaScriptアラートが発生しないことを確認する ▸ ④ wp_posts.url フィールドに `javascript:alert('XSS-18')` を設定し、HTMLソースの href 属性でエスケープされていることを確認する ▸ ⑤ `target="_blank"` のリンクに `rel="noopener noreferrer"` が付与されていることをHTMLソースで確認する</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(1) `&lt;img src=x onerror=alert('XSS-18')&gt;` ※ wp_posts.post_title に設定 / (2) `javascript:alert('XSS-18')` ※ wp_posts.url に設定</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>アラートが発生しない。ニュースタイトルが `&amp;lt;img&amp;gt;` にエスケープされ、URLの `javascript:` が無効化されて表示される</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>cp-content 補足資料対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>XSS-19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>XSS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>受講者サイト</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>サイドバー ログインフォーム（ログイン前）cp-content: sidebar-2.php</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>—（cp-content）</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>① ログイン前の状態で受講者サイトのサイドバーが表示されるページを開く ▸ ② ページのHTMLソースを表示する（Ctrl+U） ▸ ③ サイドバーのログインフォームの action 属性を確認する ▸ ④ action 属性のドメイン部分が htmlspecialchars() によりエスケープされた形式になっていることを確認する（例: `&lt;`, `&gt;`, `"` 等の HTML 特殊文字が含まれないこと）</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>—（HTMLソース確認のみ）</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>action 属性の `$_SERVER['SERVER_NAME']` 出力部分が htmlspecialchars() でエスケープされている</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>cp-content 補足資料対応（Host Header Injection 対策）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
